--- a/reports/history/android/build-24/Excel/Automation_Test_Report.xlsx
+++ b/reports/history/android/build-24/Excel/Automation_Test_Report.xlsx
@@ -594,12 +594,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>28.43</t>
+          <t>24.02</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:31:23</t>
+          <t>2026-06-24 06:43:35</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -632,12 +632,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>33.40</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:31:45</t>
+          <t>2026-06-24 06:44:08</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>43.26</t>
+          <t>31.97</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:32:46</t>
+          <t>2026-06-24 06:44:40</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>33.52</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:33:20</t>
+          <t>2026-06-24 06:45:14</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -746,12 +746,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:33:58</t>
+          <t>2026-06-24 06:45:46</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -784,12 +784,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:34:36</t>
+          <t>2026-06-24 06:46:18</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -822,12 +822,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:35:12</t>
+          <t>2026-06-24 06:46:57</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -860,12 +860,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:35:56</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -898,12 +898,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -941,7 +941,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11657,7 +11657,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12911,7 +12911,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12949,7 +12949,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13063,7 +13063,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13747,7 +13747,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14545,7 +14545,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15305,7 +15305,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15457,7 +15457,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15571,7 +15571,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15685,7 +15685,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16065,7 +16065,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16103,7 +16103,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16255,7 +16255,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16407,7 +16407,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17053,7 +17053,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17129,7 +17129,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17471,7 +17471,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17547,7 +17547,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17775,7 +17775,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17851,7 +17851,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17965,7 +17965,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18155,7 +18155,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18307,7 +18307,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18459,7 +18459,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -18763,7 +18763,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -18801,7 +18801,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -18915,7 +18915,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -18991,7 +18991,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -19181,7 +19181,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -19333,7 +19333,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -19561,7 +19561,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -19599,7 +19599,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -19637,7 +19637,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -19789,7 +19789,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -20093,7 +20093,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -20131,7 +20131,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -20350,12 +20350,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>28.43</t>
+          <t>24.02</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:31:23</t>
+          <t>2026-06-24 06:43:35</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -20388,12 +20388,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>33.40</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:31:45</t>
+          <t>2026-06-24 06:44:08</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -20426,12 +20426,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>43.26</t>
+          <t>31.97</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:32:46</t>
+          <t>2026-06-24 06:44:40</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -20464,12 +20464,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>33.52</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:33:20</t>
+          <t>2026-06-24 06:45:14</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -20502,12 +20502,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:33:58</t>
+          <t>2026-06-24 06:45:46</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -20540,12 +20540,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:34:36</t>
+          <t>2026-06-24 06:46:18</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -20578,12 +20578,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:35:12</t>
+          <t>2026-06-24 06:46:57</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -20616,12 +20616,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:35:56</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -20654,12 +20654,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -20773,7 +20773,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -20811,7 +20811,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -20887,7 +20887,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -20963,7 +20963,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -21039,7 +21039,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -21153,7 +21153,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -21305,7 +21305,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -21343,7 +21343,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -21419,7 +21419,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -21495,7 +21495,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -21571,7 +21571,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -21647,7 +21647,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -21685,7 +21685,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -21723,7 +21723,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -21875,7 +21875,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -21913,7 +21913,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -21951,7 +21951,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -21989,7 +21989,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -22065,7 +22065,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -22103,7 +22103,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -22141,7 +22141,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -22217,7 +22217,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -22293,7 +22293,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -22521,7 +22521,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -22597,7 +22597,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -22635,7 +22635,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -22711,7 +22711,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -22749,7 +22749,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -22787,7 +22787,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -22825,7 +22825,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -22901,7 +22901,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -22939,7 +22939,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -22977,7 +22977,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -23015,7 +23015,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -23053,7 +23053,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -23091,7 +23091,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -23167,7 +23167,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -23243,7 +23243,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -23319,7 +23319,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -23395,7 +23395,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -23509,7 +23509,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -23547,7 +23547,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -23585,7 +23585,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -23699,7 +23699,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -23737,7 +23737,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -23813,7 +23813,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -23851,7 +23851,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -23889,7 +23889,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -23927,7 +23927,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -23965,7 +23965,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -24003,7 +24003,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -24041,7 +24041,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -24079,7 +24079,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -24193,7 +24193,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -24231,7 +24231,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -24307,7 +24307,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -24345,7 +24345,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -24383,7 +24383,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -24421,7 +24421,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -24535,7 +24535,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -24573,7 +24573,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -24611,7 +24611,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -24687,7 +24687,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -24763,7 +24763,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -24839,7 +24839,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -24877,7 +24877,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -24953,7 +24953,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -24991,7 +24991,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -25029,7 +25029,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -25105,7 +25105,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -25219,7 +25219,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -25295,7 +25295,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -25333,7 +25333,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -25371,7 +25371,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -25409,7 +25409,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -25447,7 +25447,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -25485,7 +25485,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -25523,7 +25523,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -25637,7 +25637,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -25713,7 +25713,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -25789,7 +25789,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -25827,7 +25827,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -25903,7 +25903,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -26017,7 +26017,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -26055,7 +26055,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -26169,7 +26169,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -26207,7 +26207,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -26245,7 +26245,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -26359,7 +26359,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -26397,7 +26397,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -26435,7 +26435,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -26511,7 +26511,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -26549,7 +26549,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -26587,7 +26587,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -26625,7 +26625,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -26701,7 +26701,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -26815,7 +26815,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -26853,7 +26853,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -26891,7 +26891,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -26929,7 +26929,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -26967,7 +26967,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -27043,7 +27043,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -27119,7 +27119,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -27157,7 +27157,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -27271,7 +27271,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -27309,7 +27309,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -27347,7 +27347,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -27385,7 +27385,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -27423,7 +27423,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -27461,7 +27461,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -27499,7 +27499,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -27537,7 +27537,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:03</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -27575,7 +27575,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -27613,7 +27613,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -27651,7 +27651,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -27689,7 +27689,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -27727,7 +27727,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -27765,7 +27765,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -27955,7 +27955,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -28107,7 +28107,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -28145,7 +28145,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -28183,7 +28183,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -28221,7 +28221,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -28259,7 +28259,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -28297,7 +28297,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -28411,7 +28411,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -28487,7 +28487,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -28525,7 +28525,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -28563,7 +28563,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -28639,7 +28639,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -28715,7 +28715,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -28753,7 +28753,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -28905,7 +28905,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -29019,7 +29019,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -29057,7 +29057,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -29095,7 +29095,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -29133,7 +29133,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -29171,7 +29171,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -29209,7 +29209,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -29247,7 +29247,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -29323,7 +29323,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -29399,7 +29399,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -29437,7 +29437,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -29475,7 +29475,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -29513,7 +29513,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -29551,7 +29551,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -29703,7 +29703,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -29855,7 +29855,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -29893,7 +29893,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -29931,7 +29931,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -30007,7 +30007,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -30083,7 +30083,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -30121,7 +30121,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -30159,7 +30159,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -30197,7 +30197,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -30235,7 +30235,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -30273,7 +30273,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -30311,7 +30311,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -30349,7 +30349,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -30425,7 +30425,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -30463,7 +30463,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -30501,7 +30501,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -30615,7 +30615,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -30729,7 +30729,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -30767,7 +30767,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -30805,7 +30805,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -30881,7 +30881,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -30919,7 +30919,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -30957,7 +30957,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -30995,7 +30995,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -31033,7 +31033,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -31071,7 +31071,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -31109,7 +31109,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -31147,7 +31147,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -31185,7 +31185,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -31223,7 +31223,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -31261,7 +31261,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -31299,7 +31299,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -31375,7 +31375,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -31451,7 +31451,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -31603,7 +31603,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -31641,7 +31641,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -31679,7 +31679,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -31717,7 +31717,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -31755,7 +31755,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -31793,7 +31793,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -31831,7 +31831,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -31869,7 +31869,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -31907,7 +31907,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -31945,7 +31945,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -31983,7 +31983,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -32021,7 +32021,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -32059,7 +32059,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -32097,7 +32097,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -32135,7 +32135,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -32173,7 +32173,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -32211,7 +32211,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -32249,7 +32249,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -32325,7 +32325,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -32363,7 +32363,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -32553,7 +32553,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -32591,7 +32591,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -32629,7 +32629,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -32743,7 +32743,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -32819,7 +32819,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -32857,7 +32857,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -32933,7 +32933,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -32971,7 +32971,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -33085,7 +33085,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -33123,7 +33123,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -33161,7 +33161,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -33199,7 +33199,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -33237,7 +33237,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -33275,7 +33275,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -33351,7 +33351,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -33427,7 +33427,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -33503,7 +33503,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -33541,7 +33541,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -33579,7 +33579,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -33617,7 +33617,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -33655,7 +33655,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -33693,7 +33693,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -33731,7 +33731,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -33769,7 +33769,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -33807,7 +33807,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -33883,7 +33883,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -33959,7 +33959,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -33997,7 +33997,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -34035,7 +34035,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -34111,7 +34111,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -34149,7 +34149,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -34225,7 +34225,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -34263,7 +34263,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -34339,7 +34339,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -34377,7 +34377,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -34415,7 +34415,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -34453,7 +34453,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -34491,7 +34491,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -34567,7 +34567,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -34605,7 +34605,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -34643,7 +34643,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -34681,7 +34681,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -34719,7 +34719,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -34757,7 +34757,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -34795,7 +34795,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -34833,7 +34833,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -34871,7 +34871,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -34909,7 +34909,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -34947,7 +34947,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -34985,7 +34985,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -35023,7 +35023,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -35099,7 +35099,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -35137,7 +35137,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -35175,7 +35175,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -35213,7 +35213,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -35251,7 +35251,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -35327,7 +35327,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -35403,7 +35403,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -35441,7 +35441,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -35479,7 +35479,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -35517,7 +35517,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -35555,7 +35555,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -35593,7 +35593,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -35631,7 +35631,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -35669,7 +35669,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -35707,7 +35707,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -35745,7 +35745,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -35821,7 +35821,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -35859,7 +35859,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -35897,7 +35897,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -35973,7 +35973,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -36011,7 +36011,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -36087,7 +36087,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -36163,7 +36163,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -36201,7 +36201,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -36239,7 +36239,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -36277,7 +36277,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -36315,7 +36315,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -36353,7 +36353,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -36391,7 +36391,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -36429,7 +36429,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -36467,7 +36467,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -36581,7 +36581,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -36619,7 +36619,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -36657,7 +36657,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -36695,7 +36695,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -36733,7 +36733,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -36771,7 +36771,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -36847,7 +36847,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -36885,7 +36885,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -36961,7 +36961,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -36999,7 +36999,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -37075,7 +37075,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -37113,7 +37113,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -37189,7 +37189,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -37227,7 +37227,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -37265,7 +37265,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -37303,7 +37303,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -37341,7 +37341,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -37417,7 +37417,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -37455,7 +37455,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -37493,7 +37493,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -37569,7 +37569,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -37607,7 +37607,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -37645,7 +37645,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -37721,7 +37721,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -37759,7 +37759,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -37797,7 +37797,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -37835,7 +37835,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -37873,7 +37873,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -37911,7 +37911,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -37987,7 +37987,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -38025,7 +38025,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -38063,7 +38063,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -38101,7 +38101,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -38139,7 +38139,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -38177,7 +38177,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -38215,7 +38215,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -38253,7 +38253,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -38329,7 +38329,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -38367,7 +38367,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -38405,7 +38405,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -38443,7 +38443,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -38519,7 +38519,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -38557,7 +38557,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -38595,7 +38595,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -38671,7 +38671,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -38709,7 +38709,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -38747,7 +38747,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -38823,7 +38823,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -38899,7 +38899,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -38937,7 +38937,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -38975,7 +38975,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -39013,7 +39013,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -39051,7 +39051,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -39089,7 +39089,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -39127,7 +39127,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -39165,7 +39165,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -39203,7 +39203,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -39241,7 +39241,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -39279,7 +39279,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -39317,7 +39317,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -39355,7 +39355,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -39393,7 +39393,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -39431,7 +39431,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -39469,7 +39469,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -39507,7 +39507,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -39583,7 +39583,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -39621,7 +39621,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -39659,7 +39659,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -39697,7 +39697,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -39735,7 +39735,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -39811,7 +39811,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -39849,7 +39849,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -39887,7 +39887,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -40001,7 +40001,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:04</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -40272,7 +40272,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-06-23 09:36:05</t>
+          <t>2026-06-24 06:47:35</t>
         </is>
       </c>
     </row>
